--- a/Data/indicator_metadata.xlsx
+++ b/Data/indicator_metadata.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitednations-my.sharepoint.com/personal/alexis_athens_un_org/Documents/Documentos/CEPALSTAT Data Process/cepalstat-data-upload/Data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_12D7453E75FACAE84BE792673F6D76C005BD3D46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7224CB3D-72D0-46A9-81F8-A87DB3BC0815}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="208">
   <si>
     <t>id</t>
   </si>
@@ -37,10 +31,16 @@
     <t>cat3</t>
   </si>
   <si>
+    <t>source_id</t>
+  </si>
+  <si>
     <t>source</t>
   </si>
   <si>
-    <t>dimensions</t>
+    <t>dim_id</t>
+  </si>
+  <si>
+    <t>dimension</t>
   </si>
   <si>
     <t>yearbook</t>
@@ -88,13 +88,16 @@
     <t>sdg</t>
   </si>
   <si>
-    <t>Country area</t>
+    <t>Country area, by area type</t>
   </si>
   <si>
     <t>Geological and geographical information</t>
   </si>
   <si>
-    <t>Type of area</t>
+    <t>21899</t>
+  </si>
+  <si>
+    <t>Area type</t>
   </si>
   <si>
     <t>Area of inland waters</t>
@@ -130,6 +133,9 @@
     <t>ECLAC</t>
   </si>
   <si>
+    <t>223655; 224796</t>
+  </si>
+  <si>
     <t>Land coverage; Minor administrative division</t>
   </si>
   <si>
@@ -139,6 +145,9 @@
     <t>Landscape heterogeneity index (subnational)</t>
   </si>
   <si>
+    <t>224796</t>
+  </si>
+  <si>
     <t>Minor administrative division</t>
   </si>
   <si>
@@ -163,7 +172,10 @@
     <t>Forests</t>
   </si>
   <si>
-    <t>Type of forest</t>
+    <t>20722</t>
+  </si>
+  <si>
+    <t>Forest type</t>
   </si>
   <si>
     <t>Forest area as a proportion of total land area, by type of forest</t>
@@ -178,8 +190,7 @@
     <t>Forest extent (subnational)</t>
   </si>
   <si>
-    <t xml:space="preserve">Extent of forest loss (subnational)
-</t>
+    <t>Extent of forest loss (subnational)</t>
   </si>
   <si>
     <t>Extent of forest gain (subnational)</t>
@@ -197,6 +208,9 @@
     <t>Air quality</t>
   </si>
   <si>
+    <t>74476</t>
+  </si>
+  <si>
     <t>Location</t>
   </si>
   <si>
@@ -206,7 +220,7 @@
     <t>Fresh water quality</t>
   </si>
   <si>
-    <t>Energy production</t>
+    <t>Energy production, by energy product</t>
   </si>
   <si>
     <t>Environmental resources and their use</t>
@@ -218,37 +232,43 @@
     <t>Production, trade and consumption of energy</t>
   </si>
   <si>
-    <t>OLADE</t>
-  </si>
-  <si>
-    <t>Type of energy__Primary_and_Secondary</t>
+    <t>OLACDE</t>
+  </si>
+  <si>
+    <t>44966</t>
+  </si>
+  <si>
+    <t>Energy product by primary/secondary</t>
   </si>
   <si>
     <t>this used to be indicator 2040</t>
   </si>
   <si>
-    <t>Primary and secondary energy supply</t>
-  </si>
-  <si>
-    <t>Final energy consumption</t>
+    <t>Total energy supply, by energy product</t>
+  </si>
+  <si>
+    <t>Final energy consumption, by energy product</t>
   </si>
   <si>
     <t>this used to be indicator 2041</t>
   </si>
   <si>
-    <t>Primary energy supply from renewable and non-renewable sources, by type of energy</t>
+    <t>Primary energy supply from renewable and non-renewable sources, by energy product</t>
   </si>
   <si>
     <t>Renewable energy</t>
   </si>
   <si>
-    <t>Renewable and non-renewable primary energy type</t>
+    <t>44959</t>
+  </si>
+  <si>
+    <t>Energy product by renewability</t>
   </si>
   <si>
     <t>Renewable energy share of primary energy supply</t>
   </si>
   <si>
-    <t>Composition of renewable primary energy supply, by type of energy</t>
+    <t>Composition of renewable primary energy supply, by energy product</t>
   </si>
   <si>
     <t>Renewable energy share in the total final energy consumption (%) EG_FEC_RNEW</t>
@@ -272,7 +292,10 @@
     <t>Energy intensity measured in terms of final energy consumption and GDP, by economic activity</t>
   </si>
   <si>
-    <t>Energy intensity_Economic activity</t>
+    <t>78134</t>
+  </si>
+  <si>
+    <t>Economic activity</t>
   </si>
   <si>
     <t>Installed electricity-generating capacity, by energy source</t>
@@ -281,7 +304,10 @@
     <t>Electricity</t>
   </si>
   <si>
-    <t>Type of energy source</t>
+    <t>77605</t>
+  </si>
+  <si>
+    <t>Electricity source</t>
   </si>
   <si>
     <t>Installed electricity-generating capacity (historical series)</t>
@@ -299,7 +325,7 @@
     <t>Electricity losses as a proportion of total electricity supply</t>
   </si>
   <si>
-    <t>Public investment in renewable energy</t>
+    <t>Public investment in renewable energy, by energy source</t>
   </si>
   <si>
     <t>Energy investment and subsidies</t>
@@ -308,7 +334,10 @@
     <t>IRENA</t>
   </si>
   <si>
-    <t>Type of renewable energy</t>
+    <t>78139</t>
+  </si>
+  <si>
+    <t>Renewable energy type</t>
   </si>
   <si>
     <t>Fossil-fuel subsidies (consumption and production) (billions of nominal United States dollars) ER_FFS_CMPT_CD</t>
@@ -332,178 +361,214 @@
     <t>Agricultural area, by type of land use</t>
   </si>
   <si>
-    <t>Type of agricultural land</t>
+    <t>26646</t>
+  </si>
+  <si>
+    <t>Agricultural land type</t>
   </si>
   <si>
     <t>Proportion of agricultural area under organic farming</t>
   </si>
   <si>
+    <t>Capture fisheries production, by fishery type</t>
+  </si>
+  <si>
+    <t>Biological resources</t>
+  </si>
+  <si>
+    <t>Aquatic resources</t>
+  </si>
+  <si>
+    <t>20720</t>
+  </si>
+  <si>
+    <t>Fishery type</t>
+  </si>
+  <si>
+    <t>Aquaculture production, by water type</t>
+  </si>
+  <si>
+    <t>26819</t>
+  </si>
+  <si>
+    <t>Water type</t>
+  </si>
+  <si>
+    <t>Harvested area, by crop</t>
+  </si>
+  <si>
+    <t>Crops</t>
+  </si>
+  <si>
+    <t>20721</t>
+  </si>
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>Fertilizer consumption</t>
+  </si>
+  <si>
+    <t>Fertilizer use intensity</t>
+  </si>
+  <si>
+    <t>Pesticide consumption, by type of pesticide</t>
+  </si>
+  <si>
+    <t>20723</t>
+  </si>
+  <si>
+    <t>Pesticide type</t>
+  </si>
+  <si>
+    <t>Pesticide use intensity</t>
+  </si>
+  <si>
+    <t>Level of water stress: freshwater withdrawal as a proportion of available freshwater resources (%) ER_H2O_STRESS</t>
+  </si>
+  <si>
+    <t>Water resources</t>
+  </si>
+  <si>
+    <t>77571</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Water withdrawal, by sector</t>
+  </si>
+  <si>
+    <t>Abstraction, use and returns of water</t>
+  </si>
+  <si>
+    <t>59252</t>
+  </si>
+  <si>
+    <t>Sector_Water</t>
+  </si>
+  <si>
+    <t>Water intensity of agricultural value added</t>
+  </si>
+  <si>
+    <t>Water Use Efficiency (United States dollars per cubic meter) ER_H2O_WUEYST</t>
+  </si>
+  <si>
+    <t>Degree of integrated water resources management implementation (%) ER_H2O_IWRMD</t>
+  </si>
+  <si>
+    <t>74666</t>
+  </si>
+  <si>
+    <t>Level/Status</t>
+  </si>
+  <si>
+    <t>Share of global greenhouse gas (GHG) emissions</t>
+  </si>
+  <si>
+    <t>Residuals</t>
+  </si>
+  <si>
+    <t>Emissions to air</t>
+  </si>
+  <si>
+    <t>Emissions of greenhouse gases (GHGs)</t>
+  </si>
+  <si>
+    <t>WRI</t>
+  </si>
+  <si>
+    <t>Greenhouse gas (GHG) emissions, by sector</t>
+  </si>
+  <si>
+    <t>63371</t>
+  </si>
+  <si>
+    <t>Sector_GHG</t>
+  </si>
+  <si>
+    <t>Greenhouse gas (GHG) emissions, by energy subsector</t>
+  </si>
+  <si>
+    <t>84302</t>
+  </si>
+  <si>
+    <t>Energy subsector</t>
+  </si>
+  <si>
+    <t>Greenhouse gas (GHG) emissions per unit of GDP</t>
+  </si>
+  <si>
+    <t>Greenhouse gas (GHG) emissions per capita</t>
+  </si>
+  <si>
+    <t>Carbon dioxide (CO2) emissions excluding land-use change and forestry</t>
+  </si>
+  <si>
+    <t>Share of global carbon dioxide (CO2) emissions</t>
+  </si>
+  <si>
+    <t>Carbon dioxide (CO2) emissions per unit of GDP</t>
+  </si>
+  <si>
+    <t>Carbon dioxide (CO2) emissions per capita</t>
+  </si>
+  <si>
+    <t>Consumption of ozone-depleting substances (ODS), by ODS</t>
+  </si>
+  <si>
+    <t>Consumption of ozone depleting substances (ODS)</t>
+  </si>
+  <si>
+    <t>UNEP</t>
+  </si>
+  <si>
+    <t>26657</t>
+  </si>
+  <si>
+    <t>Ozone-depleting substance</t>
+  </si>
+  <si>
+    <t>Proportion of safely treated domestic wastewater flows (%) EN_WWT_WWDS</t>
+  </si>
+  <si>
+    <t>Generation and management of wastewater</t>
+  </si>
+  <si>
+    <t>Collection and treatment of wastewater</t>
+  </si>
+  <si>
+    <t>Municipal waste recycled (Tonnes) EN_MWT_RCYV</t>
+  </si>
+  <si>
+    <t>Generation and management of waste</t>
+  </si>
+  <si>
+    <t>Management of waste</t>
+  </si>
+  <si>
+    <t>Electronic waste recycled (Tonnes) EN_EWT_RCYV</t>
+  </si>
+  <si>
+    <t>Number of disaster events, by type of disaster</t>
+  </si>
+  <si>
+    <t>Extreme events and disasters</t>
+  </si>
+  <si>
+    <t>Natural extreme events and disasters</t>
+  </si>
+  <si>
+    <t>Occurrence of natural extreme events and disasters</t>
+  </si>
+  <si>
     <t>CRED</t>
   </si>
   <si>
-    <t>Capture fisheries production</t>
-  </si>
-  <si>
-    <t>Biological resources</t>
-  </si>
-  <si>
-    <t>Aquatic resources</t>
-  </si>
-  <si>
-    <t>Type of fishery</t>
-  </si>
-  <si>
-    <t>Aquaculture production</t>
-  </si>
-  <si>
-    <t>Aquaculture production area</t>
-  </si>
-  <si>
-    <t>Harvested area of main crops</t>
-  </si>
-  <si>
-    <t>Crops</t>
-  </si>
-  <si>
-    <t>Crop</t>
-  </si>
-  <si>
-    <t>Fertilizer consumption</t>
-  </si>
-  <si>
-    <t>Fertilizer use intensity</t>
-  </si>
-  <si>
-    <t>Pesticide consumption</t>
-  </si>
-  <si>
-    <t>Type of Pesticide</t>
-  </si>
-  <si>
-    <t>Pesticide use intensity</t>
-  </si>
-  <si>
-    <t>Level of water stress: freshwater withdrawal as a proportion of available freshwater resources (%) ER_H2O_STRESS</t>
-  </si>
-  <si>
-    <t>Water resources</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Water withdrawal, by sector</t>
-  </si>
-  <si>
-    <t>Abstraction, use and returns of water</t>
-  </si>
-  <si>
-    <t>Sector__Water resources</t>
-  </si>
-  <si>
-    <t>Water intensity of agricultural value added</t>
-  </si>
-  <si>
-    <t>Water Use Efficiency (United States dollars per cubic meter) ER_H2O_WUEYST</t>
-  </si>
-  <si>
-    <t>Degree of integrated water resources management implementation (%) ER_H2O_IWRMD</t>
-  </si>
-  <si>
-    <t>Level/Status</t>
-  </si>
-  <si>
-    <t>Share of global greenhouse gas (GHG) emissions</t>
-  </si>
-  <si>
-    <t>Residuals</t>
-  </si>
-  <si>
-    <t>Emissions to air</t>
-  </si>
-  <si>
-    <t>Emissions of greenhouse gases (GHGs)</t>
-  </si>
-  <si>
-    <t>CAIT - WRI</t>
-  </si>
-  <si>
-    <t>Greenhouse gas (GHG) emissions, by sector</t>
-  </si>
-  <si>
-    <t>Greenhouse Gas (GHG) Emissions by sector</t>
-  </si>
-  <si>
-    <t>Greenhouse gas (GHG) emissions from the energy sector</t>
-  </si>
-  <si>
-    <t>Greenhouse Gas (GHG) Emissions of the energy sector</t>
-  </si>
-  <si>
-    <t>Greenhouse gas (GHG) emissions per unit of GDP</t>
-  </si>
-  <si>
-    <t>Greenhouse gas (GHG) emissions per capita</t>
-  </si>
-  <si>
-    <t>Carbon dioxide (CO2) emissions, excluding land-use change and forestry</t>
-  </si>
-  <si>
-    <t>Share of global carbon dioxide (CO2) emissions</t>
-  </si>
-  <si>
-    <t>Carbon dioxide (CO2) emissions per unit of GDP</t>
-  </si>
-  <si>
-    <t>Carbon dioxide (CO2) emissions per capita</t>
-  </si>
-  <si>
-    <t>Consumption of all ozone-depleting substances (ODS)</t>
-  </si>
-  <si>
-    <t>Consumption of ozone depleting substances (ODS)</t>
-  </si>
-  <si>
-    <t>UNEP</t>
-  </si>
-  <si>
-    <t>Type of ozone depleting substances (ODS)</t>
-  </si>
-  <si>
-    <t>Proportion of safely treated domestic wastewater flows (%) EN_WWT_WWDS</t>
-  </si>
-  <si>
-    <t>Generation and management of wastewater</t>
-  </si>
-  <si>
-    <t>Collection and treatment of wastewater</t>
-  </si>
-  <si>
-    <t>Municipal waste recycled (Tonnes) EN_MWT_RCYV</t>
-  </si>
-  <si>
-    <t>Generation and management of waste</t>
-  </si>
-  <si>
-    <t>Management of waste</t>
-  </si>
-  <si>
-    <t>Electronic waste recycled (Tonnes) EN_EWT_RCYV</t>
-  </si>
-  <si>
-    <t>Number of disaster events, by type of disaster</t>
-  </si>
-  <si>
-    <t>Extreme events and disasters</t>
-  </si>
-  <si>
-    <t>Natural extreme events and disasters</t>
-  </si>
-  <si>
-    <t>Occurrence of natural extreme events and disasters</t>
-  </si>
-  <si>
-    <t>Type of disaster</t>
+    <t>21714</t>
+  </si>
+  <si>
+    <t>Disaster type</t>
   </si>
   <si>
     <t>Number of deaths attributed to disasters, by type of disaster</t>
@@ -515,8 +580,7 @@
     <t>Number of directly affected persons attributed to disasters, by type of disaster</t>
   </si>
   <si>
-    <t xml:space="preserve">Economic loss attributed to disasters, by type of disaster
-</t>
+    <t>Economic loss attributed to disasters, by type of disaster</t>
   </si>
   <si>
     <t>Proportion of population with primary reliance on clean fuels and technology (%) EG_EGY_CLEAN</t>
@@ -549,13 +613,16 @@
     <t>ISO 14001-certified enterprises per unit of GDP</t>
   </si>
   <si>
-    <t>Multilateral environmental agreements</t>
+    <t>Multilateral environmental agreements, by status</t>
   </si>
   <si>
     <t>Participation in MEAs and environmental conventions</t>
   </si>
   <si>
     <t>InforMEA</t>
+  </si>
+  <si>
+    <t>26667; 26689</t>
   </si>
   <si>
     <t>Multilateral environmental agreements; Signature, party, entry into force</t>
@@ -576,8 +643,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,21 +692,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -677,7 +736,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -711,7 +770,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -746,10 +804,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -922,11 +979,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K84"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M84"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -960,2274 +1017,2631 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>3381</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>16</v>
+      <c r="F2">
+        <v>651</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>4501</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <v>7189</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>2035</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>651</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>2054</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="F5">
+        <v>651</v>
+      </c>
+      <c r="G5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>3974</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>9083</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>4176</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>651</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>2016</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>876</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>3355</v>
       </c>
       <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
+      <c r="F9">
+        <v>651</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>5417</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F10">
+        <v>9362</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>5418</v>
       </c>
       <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>9362</v>
+      </c>
+      <c r="G11" t="s">
         <v>38</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>3963</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" t="s">
-        <v>16</v>
+        <v>46</v>
+      </c>
+      <c r="F12">
+        <v>15911</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>3967</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" t="s">
-        <v>16</v>
+        <v>46</v>
+      </c>
+      <c r="F13">
+        <v>15911</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>3968</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" t="s">
-        <v>16</v>
+        <v>46</v>
+      </c>
+      <c r="F14">
+        <v>15911</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>3979</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" t="s">
-        <v>16</v>
+        <v>46</v>
+      </c>
+      <c r="F15">
+        <v>5154</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>2036</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
+        <v>51</v>
+      </c>
+      <c r="F16">
+        <v>651</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>52</v>
+      </c>
+      <c r="I16" t="s">
+        <v>53</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>2021</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>1338</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>2530</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>16</v>
+        <v>51</v>
+      </c>
+      <c r="F18">
+        <v>1338</v>
+      </c>
+      <c r="G18" t="s">
+        <v>38</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>2531</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" t="s">
-        <v>16</v>
+        <v>51</v>
+      </c>
+      <c r="F19">
+        <v>5174</v>
+      </c>
+      <c r="G19" t="s">
+        <v>17</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>5423</v>
       </c>
       <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
         <v>51</v>
       </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>35</v>
+      <c r="F20">
+        <v>9362</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="H20" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>5424</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="F21">
+        <v>9362</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="H21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>5425</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="F22">
+        <v>9362</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="H22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>5422</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="F23">
+        <v>9362</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="H23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24">
         <v>3946</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" t="s">
-        <v>20</v>
+        <v>63</v>
+      </c>
+      <c r="F24">
+        <v>5188</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>64</v>
+      </c>
+      <c r="I24" t="s">
+        <v>65</v>
       </c>
       <c r="J24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25">
         <v>3850</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="F25">
+        <v>9747</v>
+      </c>
+      <c r="G25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26">
         <v>5672</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="F26">
+        <v>714</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
-      </c>
-      <c r="J26" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+      <c r="H26" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s">
+        <v>74</v>
+      </c>
+      <c r="L26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27">
         <v>2487</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="F27">
+        <v>714</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K27" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28">
         <v>5730</v>
       </c>
       <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
         <v>69</v>
       </c>
-      <c r="C28" t="s">
-        <v>62</v>
-      </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="F28">
+        <v>714</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
-      </c>
-      <c r="J28" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+      <c r="H28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s">
+        <v>74</v>
+      </c>
+      <c r="L28" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29">
         <v>2486</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29">
+        <v>714</v>
+      </c>
+      <c r="G29" t="s">
         <v>72</v>
       </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" t="s">
-        <v>73</v>
-      </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>81</v>
+      </c>
+      <c r="I29" t="s">
+        <v>82</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30">
         <v>3154</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30">
+        <v>714</v>
+      </c>
+      <c r="G30" t="s">
         <v>72</v>
       </c>
-      <c r="F30" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" t="s">
-        <v>16</v>
-      </c>
       <c r="J30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31">
         <v>4236</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31">
+        <v>714</v>
+      </c>
+      <c r="G31" t="s">
         <v>72</v>
       </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31" t="s">
-        <v>73</v>
-      </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32">
         <v>3883</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s">
-        <v>16</v>
+        <v>80</v>
+      </c>
+      <c r="F32">
+        <v>16027</v>
+      </c>
+      <c r="G32" t="s">
+        <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33">
         <v>4174</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>78</v>
-      </c>
-      <c r="F33" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s">
-        <v>16</v>
+        <v>87</v>
+      </c>
+      <c r="F33">
+        <v>885</v>
+      </c>
+      <c r="G33" t="s">
+        <v>72</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34">
         <v>4183</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-      <c r="I34" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+      <c r="F34">
+        <v>10685</v>
+      </c>
+      <c r="G34" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35">
         <v>2023</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E35" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-      <c r="H35" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" t="s">
-        <v>16</v>
+        <v>87</v>
+      </c>
+      <c r="F35">
+        <v>714</v>
+      </c>
+      <c r="G35" t="s">
+        <v>72</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36">
         <v>4184</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
-      </c>
-      <c r="I36" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+      <c r="F36">
+        <v>10685</v>
+      </c>
+      <c r="G36" t="s">
+        <v>72</v>
+      </c>
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37">
         <v>4243</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" t="s">
-        <v>35</v>
+        <v>87</v>
+      </c>
+      <c r="F37">
+        <v>885</v>
       </c>
       <c r="G37" t="s">
-        <v>83</v>
+        <v>72</v>
+      </c>
+      <c r="H37" t="s">
+        <v>92</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="K37" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38">
         <v>4150</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
+        <v>95</v>
+      </c>
+      <c r="F38">
+        <v>714</v>
       </c>
       <c r="G38" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39">
         <v>1755</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39" t="s">
-        <v>16</v>
-      </c>
-      <c r="J39" t="s">
-        <v>17</v>
+        <v>95</v>
+      </c>
+      <c r="F39">
+        <v>714</v>
+      </c>
+      <c r="G39" t="s">
+        <v>72</v>
       </c>
       <c r="K39" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L39" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40">
         <v>1754</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-      <c r="H40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" t="s">
-        <v>16</v>
+        <v>95</v>
+      </c>
+      <c r="F40">
+        <v>714</v>
+      </c>
+      <c r="G40" t="s">
+        <v>72</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41">
         <v>4234</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E41" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-      <c r="I41" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="F41">
+        <v>714</v>
+      </c>
+      <c r="G41" t="s">
+        <v>72</v>
+      </c>
+      <c r="K41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42">
         <v>4235</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-      <c r="H42" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" t="s">
-        <v>16</v>
+        <v>95</v>
+      </c>
+      <c r="F42">
+        <v>714</v>
+      </c>
+      <c r="G42" t="s">
+        <v>72</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K42" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43">
         <v>4244</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" t="s">
-        <v>94</v>
+        <v>104</v>
+      </c>
+      <c r="F43">
+        <v>10686</v>
       </c>
       <c r="G43" t="s">
-        <v>95</v>
+        <v>105</v>
+      </c>
+      <c r="H43" t="s">
+        <v>106</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+      <c r="K43" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44">
         <v>4826</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="F44">
+        <v>9461</v>
+      </c>
+      <c r="G44" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45">
         <v>4375</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E45" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" t="s">
-        <v>20</v>
-      </c>
-      <c r="J45" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="F45">
+        <v>16068</v>
+      </c>
+      <c r="G45" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46">
         <v>4827</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E46" t="s">
-        <v>93</v>
-      </c>
-      <c r="F46" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="F46">
+        <v>5676</v>
+      </c>
+      <c r="G46" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47">
         <v>1739</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
-      </c>
-      <c r="F47" t="s">
-        <v>15</v>
-      </c>
-      <c r="J47" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47">
+        <v>651</v>
+      </c>
+      <c r="G47" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48">
         <v>1869</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E48" t="s">
-        <v>101</v>
-      </c>
-      <c r="F48" t="s">
-        <v>15</v>
+        <v>113</v>
+      </c>
+      <c r="F48">
+        <v>651</v>
       </c>
       <c r="G48" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="J48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K48" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>4049</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E49" t="s">
-        <v>101</v>
-      </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" t="s">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="F49">
+        <v>651</v>
+      </c>
+      <c r="G49" t="s">
+        <v>17</v>
       </c>
       <c r="J49" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>2019</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E50" t="s">
-        <v>108</v>
-      </c>
-      <c r="F50" t="s">
-        <v>15</v>
+        <v>120</v>
+      </c>
+      <c r="F50">
+        <v>877</v>
       </c>
       <c r="G50" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="I50" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K50" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>2020</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E51" t="s">
-        <v>108</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
+        <v>120</v>
+      </c>
+      <c r="F51">
+        <v>877</v>
       </c>
       <c r="G51" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="I51" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="J51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K51" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>1740</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E52" t="s">
-        <v>113</v>
-      </c>
-      <c r="F52" t="s">
-        <v>15</v>
+        <v>127</v>
+      </c>
+      <c r="F52">
+        <v>651</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="I52" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K52" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>2038</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E53" t="s">
-        <v>113</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" t="s">
+        <v>127</v>
+      </c>
+      <c r="F53">
+        <v>651</v>
+      </c>
+      <c r="G53" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>2022</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E54" t="s">
-        <v>113</v>
-      </c>
-      <c r="F54" t="s">
-        <v>35</v>
-      </c>
-      <c r="H54" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" t="s">
-        <v>16</v>
+        <v>127</v>
+      </c>
+      <c r="F54">
+        <v>913</v>
+      </c>
+      <c r="G54" t="s">
+        <v>38</v>
       </c>
       <c r="J54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K54" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>2039</v>
       </c>
       <c r="B55" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>113</v>
-      </c>
-      <c r="F55" t="s">
-        <v>35</v>
+        <v>127</v>
+      </c>
+      <c r="F55">
+        <v>1827</v>
       </c>
       <c r="G55" t="s">
-        <v>118</v>
+        <v>38</v>
+      </c>
+      <c r="H55" t="s">
+        <v>133</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+      <c r="K55" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56">
         <v>3382</v>
       </c>
       <c r="B56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" t="s">
         <v>119</v>
       </c>
-      <c r="C56" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" t="s">
-        <v>107</v>
-      </c>
       <c r="E56" t="s">
-        <v>113</v>
-      </c>
-      <c r="F56" t="s">
-        <v>35</v>
-      </c>
-      <c r="H56" t="s">
-        <v>16</v>
+        <v>127</v>
+      </c>
+      <c r="F56">
+        <v>1827</v>
+      </c>
+      <c r="G56" t="s">
+        <v>38</v>
       </c>
       <c r="J56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57">
         <v>3853</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E57" t="s">
-        <v>121</v>
-      </c>
-      <c r="F57" t="s">
-        <v>20</v>
+        <v>137</v>
+      </c>
+      <c r="F57">
+        <v>3713</v>
       </c>
       <c r="G57" t="s">
-        <v>122</v>
-      </c>
-      <c r="J57" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="H57" t="s">
+        <v>138</v>
+      </c>
+      <c r="I57" t="s">
+        <v>139</v>
+      </c>
+      <c r="L57" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58">
         <v>4185</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D58" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E58" t="s">
-        <v>124</v>
-      </c>
-      <c r="F58" t="s">
-        <v>15</v>
+        <v>141</v>
+      </c>
+      <c r="F58">
+        <v>5173</v>
       </c>
       <c r="G58" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
+        <v>142</v>
+      </c>
+      <c r="I58" t="s">
+        <v>143</v>
       </c>
       <c r="J58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59">
         <v>4186</v>
       </c>
       <c r="B59" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
-      </c>
-      <c r="F59" t="s">
-        <v>35</v>
-      </c>
-      <c r="H59" t="s">
-        <v>16</v>
+        <v>141</v>
+      </c>
+      <c r="F59">
+        <v>1743</v>
+      </c>
+      <c r="G59" t="s">
+        <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60">
         <v>3854</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C60" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
-      </c>
-      <c r="F60" t="s">
-        <v>20</v>
+        <v>141</v>
+      </c>
+      <c r="F60">
+        <v>3713</v>
       </c>
       <c r="G60" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="H60" t="s">
-        <v>16</v>
+        <v>138</v>
+      </c>
+      <c r="I60" t="s">
+        <v>139</v>
       </c>
       <c r="J60" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61">
         <v>3855</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D61" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
-      </c>
-      <c r="F61" t="s">
-        <v>20</v>
+        <v>141</v>
+      </c>
+      <c r="F61">
+        <v>5439</v>
       </c>
       <c r="G61" t="s">
-        <v>129</v>
-      </c>
-      <c r="J61" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="H61" t="s">
+        <v>147</v>
+      </c>
+      <c r="I61" t="s">
+        <v>148</v>
+      </c>
+      <c r="L61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62">
         <v>3387</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F62" t="s">
-        <v>134</v>
-      </c>
-      <c r="J62" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+      <c r="F62">
+        <v>1742</v>
+      </c>
+      <c r="G62" t="s">
+        <v>153</v>
+      </c>
+      <c r="L62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63">
         <v>3351</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D63" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E63" t="s">
-        <v>133</v>
-      </c>
-      <c r="F63" t="s">
-        <v>134</v>
+        <v>152</v>
+      </c>
+      <c r="F63">
+        <v>1742</v>
       </c>
       <c r="G63" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="H63" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="I63" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="J63" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K63" t="s">
+        <v>18</v>
+      </c>
+      <c r="L63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64">
         <v>4462</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D64" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F64" t="s">
-        <v>134</v>
+        <v>152</v>
+      </c>
+      <c r="F64">
+        <v>1742</v>
       </c>
       <c r="G64" t="s">
-        <v>138</v>
-      </c>
-      <c r="J64" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+      <c r="H64" t="s">
+        <v>158</v>
+      </c>
+      <c r="I64" t="s">
+        <v>159</v>
+      </c>
+      <c r="L64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65">
         <v>4463</v>
       </c>
       <c r="B65" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C65" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E65" t="s">
-        <v>133</v>
-      </c>
-      <c r="F65" t="s">
-        <v>134</v>
-      </c>
-      <c r="J65" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+      <c r="F65">
+        <v>10621</v>
+      </c>
+      <c r="G65" t="s">
+        <v>153</v>
+      </c>
+      <c r="L65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66">
         <v>4461</v>
       </c>
       <c r="B66" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D66" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E66" t="s">
-        <v>133</v>
-      </c>
-      <c r="F66" t="s">
-        <v>134</v>
-      </c>
-      <c r="I66" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+      <c r="F66">
+        <v>10621</v>
+      </c>
+      <c r="G66" t="s">
+        <v>153</v>
+      </c>
+      <c r="K66" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67">
         <v>3158</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D67" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
-      </c>
-      <c r="F67" t="s">
-        <v>134</v>
-      </c>
-      <c r="H67" t="s">
-        <v>16</v>
+        <v>152</v>
+      </c>
+      <c r="F67">
+        <v>1742</v>
+      </c>
+      <c r="G67" t="s">
+        <v>153</v>
       </c>
       <c r="J67" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68">
         <v>3159</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D68" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E68" t="s">
-        <v>133</v>
-      </c>
-      <c r="F68" t="s">
-        <v>134</v>
-      </c>
-      <c r="H68" t="s">
-        <v>16</v>
+        <v>152</v>
+      </c>
+      <c r="F68">
+        <v>1742</v>
+      </c>
+      <c r="G68" t="s">
+        <v>153</v>
       </c>
       <c r="J68" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69">
         <v>5650</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C69" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D69" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E69" t="s">
-        <v>133</v>
-      </c>
-      <c r="F69" t="s">
-        <v>134</v>
-      </c>
-      <c r="H69" t="s">
-        <v>16</v>
+        <v>152</v>
+      </c>
+      <c r="F69">
+        <v>10621</v>
+      </c>
+      <c r="G69" t="s">
+        <v>153</v>
       </c>
       <c r="J69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70">
         <v>5649</v>
       </c>
       <c r="B70" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C70" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D70" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E70" t="s">
-        <v>133</v>
-      </c>
-      <c r="F70" t="s">
-        <v>134</v>
-      </c>
-      <c r="H70" t="s">
-        <v>16</v>
+        <v>152</v>
+      </c>
+      <c r="F70">
+        <v>10621</v>
+      </c>
+      <c r="G70" t="s">
+        <v>153</v>
       </c>
       <c r="J70" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71">
         <v>2037</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D71" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E71" t="s">
-        <v>146</v>
-      </c>
-      <c r="F71" t="s">
-        <v>147</v>
+        <v>167</v>
+      </c>
+      <c r="F71">
+        <v>630</v>
       </c>
       <c r="G71" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="H71" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="I71" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="J71" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K71" t="s">
+        <v>18</v>
+      </c>
+      <c r="L71" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72">
         <v>3852</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="E72" t="s">
-        <v>151</v>
-      </c>
-      <c r="F72" t="s">
-        <v>20</v>
-      </c>
-      <c r="H72" t="s">
-        <v>16</v>
+        <v>173</v>
+      </c>
+      <c r="F72">
+        <v>5437</v>
+      </c>
+      <c r="G72" t="s">
+        <v>22</v>
       </c>
       <c r="J72" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73">
         <v>4370</v>
       </c>
       <c r="B73" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C73" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D73" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E73" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="F73">
+        <v>9833</v>
+      </c>
+      <c r="G73" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74">
         <v>5113</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C74" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D74" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E74" t="s">
-        <v>154</v>
-      </c>
-      <c r="F74" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+      <c r="F74">
+        <v>8631</v>
+      </c>
+      <c r="G74" t="s">
+        <v>22</v>
+      </c>
+      <c r="L74" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75">
         <v>5647</v>
       </c>
       <c r="B75" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C75" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E75" t="s">
-        <v>159</v>
-      </c>
-      <c r="F75" t="s">
-        <v>105</v>
+        <v>181</v>
+      </c>
+      <c r="F75">
+        <v>742</v>
       </c>
       <c r="G75" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H75" t="s">
-        <v>16</v>
+        <v>183</v>
+      </c>
+      <c r="I75" t="s">
+        <v>184</v>
       </c>
       <c r="J75" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76">
         <v>5645</v>
       </c>
       <c r="B76" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C76" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="D76" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E76" t="s">
-        <v>162</v>
-      </c>
-      <c r="F76" t="s">
-        <v>105</v>
+        <v>186</v>
+      </c>
+      <c r="F76">
+        <v>742</v>
       </c>
       <c r="G76" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H76" t="s">
-        <v>16</v>
+        <v>183</v>
+      </c>
+      <c r="I76" t="s">
+        <v>184</v>
       </c>
       <c r="J76" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77">
         <v>5646</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="D77" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E77" t="s">
-        <v>162</v>
-      </c>
-      <c r="F77" t="s">
-        <v>105</v>
+        <v>186</v>
+      </c>
+      <c r="F77">
+        <v>742</v>
       </c>
       <c r="G77" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H77" t="s">
-        <v>16</v>
+        <v>183</v>
+      </c>
+      <c r="I77" t="s">
+        <v>184</v>
       </c>
       <c r="J77" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="L77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78">
         <v>4046</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="D78" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E78" t="s">
-        <v>162</v>
-      </c>
-      <c r="F78" t="s">
-        <v>105</v>
+        <v>186</v>
+      </c>
+      <c r="F78">
+        <v>742</v>
       </c>
       <c r="G78" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H78" t="s">
-        <v>16</v>
+        <v>183</v>
       </c>
       <c r="I78" t="s">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="J78" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K78" t="s">
+        <v>18</v>
+      </c>
+      <c r="L78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79">
         <v>3882</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D79" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="E79" t="s">
-        <v>168</v>
-      </c>
-      <c r="F79" t="s">
-        <v>20</v>
+        <v>192</v>
+      </c>
+      <c r="F79">
+        <v>3719</v>
       </c>
       <c r="G79" t="s">
-        <v>58</v>
-      </c>
-      <c r="J79" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="H79" t="s">
+        <v>64</v>
+      </c>
+      <c r="I79" t="s">
+        <v>65</v>
+      </c>
+      <c r="L79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80">
         <v>1763</v>
       </c>
       <c r="B80" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C80" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D80" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="E80" t="s">
-        <v>172</v>
-      </c>
-      <c r="F80" t="s">
-        <v>173</v>
-      </c>
-      <c r="I80" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="F80">
+        <v>749</v>
+      </c>
+      <c r="G80" t="s">
+        <v>197</v>
+      </c>
+      <c r="K80" t="s">
+        <v>18</v>
+      </c>
+      <c r="L80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81">
         <v>2029</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C81" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="E81" t="s">
-        <v>172</v>
-      </c>
-      <c r="F81" t="s">
-        <v>35</v>
-      </c>
-      <c r="J81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+      <c r="F81">
+        <v>882</v>
+      </c>
+      <c r="G81" t="s">
+        <v>197</v>
+      </c>
+      <c r="L81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82">
         <v>2031</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="C82" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="E82" t="s">
-        <v>176</v>
-      </c>
-      <c r="F82" t="s">
-        <v>177</v>
+        <v>200</v>
+      </c>
+      <c r="F82">
+        <v>11306</v>
       </c>
       <c r="G82" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H82" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="I82" t="s">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="J82" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="K82" t="s">
+        <v>18</v>
+      </c>
+      <c r="L82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83">
         <v>4190</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C83" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D83" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="E83" t="s">
-        <v>181</v>
-      </c>
-      <c r="F83" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+      <c r="F83">
+        <v>16002</v>
+      </c>
+      <c r="G83" t="s">
+        <v>22</v>
+      </c>
+      <c r="L83" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84">
         <v>3724</v>
       </c>
       <c r="B84" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D84" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="E84" t="s">
-        <v>181</v>
-      </c>
-      <c r="F84" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" t="s">
-        <v>21</v>
+        <v>206</v>
+      </c>
+      <c r="F84">
+        <v>16002</v>
+      </c>
+      <c r="G84" t="s">
+        <v>22</v>
+      </c>
+      <c r="L84" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{8b77875e-5908-45a0-9cb4-dec9ae074618}" enabled="1" method="Privileged" siteId="{0f9e35db-544f-4f60-bdcc-5ea416e6dc70}" removed="0"/>
-</clbl:labelList>
 </file>
--- a/Data/indicator_metadata.xlsx
+++ b/Data/indicator_metadata.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitednations-my.sharepoint.com/personal/alexis_athens_un_org/Documents/Documentos/CEPALSTAT Data Process/cepalstat-data-upload/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_789E1D78E5C9F4C8A6074CE1C33EC7942A4ABFD4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25DAAB18-81DB-45F0-BC2E-10DFD4D7B1DA}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="28815" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -643,8 +649,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,6 +662,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -681,24 +694,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -736,7 +762,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -770,6 +796,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -804,9 +831,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -979,11 +1007,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M84"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1024,7 +1052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3381</v>
       </c>
@@ -1056,7 +1084,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>4501</v>
       </c>
@@ -1082,7 +1110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2035</v>
       </c>
@@ -1120,7 +1148,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2054</v>
       </c>
@@ -1146,7 +1174,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3974</v>
       </c>
@@ -1172,7 +1200,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4176</v>
       </c>
@@ -1201,7 +1229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -1233,7 +1261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3355</v>
       </c>
@@ -1262,7 +1290,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>5417</v>
       </c>
@@ -1294,7 +1322,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>5418</v>
       </c>
@@ -1326,7 +1354,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>3963</v>
       </c>
@@ -1355,7 +1383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3967</v>
       </c>
@@ -1387,7 +1415,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>3968</v>
       </c>
@@ -1419,7 +1447,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3979</v>
       </c>
@@ -1448,7 +1476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2036</v>
       </c>
@@ -1483,7 +1511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2021</v>
       </c>
@@ -1502,7 +1530,7 @@
       <c r="F17">
         <v>1338</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H17" t="s">
@@ -1521,7 +1549,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2530</v>
       </c>
@@ -1540,7 +1568,7 @@
       <c r="F18">
         <v>1338</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J18" t="s">
@@ -1550,7 +1578,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2531</v>
       </c>
@@ -1579,7 +1607,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>5423</v>
       </c>
@@ -1611,7 +1639,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>5424</v>
       </c>
@@ -1643,7 +1671,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>5425</v>
       </c>
@@ -1675,7 +1703,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>5422</v>
       </c>
@@ -1707,7 +1735,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>3946</v>
       </c>
@@ -1742,7 +1770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>3850</v>
       </c>
@@ -1768,7 +1796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>5672</v>
       </c>
@@ -1803,7 +1831,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2487</v>
       </c>
@@ -1841,7 +1869,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>5730</v>
       </c>
@@ -1876,7 +1904,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2486</v>
       </c>
@@ -1911,7 +1939,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3154</v>
       </c>
@@ -1940,7 +1968,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>4236</v>
       </c>
@@ -1978,7 +2006,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>3883</v>
       </c>
@@ -2010,7 +2038,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>4174</v>
       </c>
@@ -2042,7 +2070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>4183</v>
       </c>
@@ -2071,7 +2099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2023</v>
       </c>
@@ -2103,7 +2131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>4184</v>
       </c>
@@ -2132,7 +2160,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>4243</v>
       </c>
@@ -2167,7 +2195,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>4150</v>
       </c>
@@ -2205,7 +2233,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1755</v>
       </c>
@@ -2237,7 +2265,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1754</v>
       </c>
@@ -2269,7 +2297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>4234</v>
       </c>
@@ -2298,7 +2326,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>4235</v>
       </c>
@@ -2330,7 +2358,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>4244</v>
       </c>
@@ -2365,7 +2393,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4826</v>
       </c>
@@ -2391,7 +2419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4375</v>
       </c>
@@ -2417,7 +2445,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4827</v>
       </c>
@@ -2443,7 +2471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1739</v>
       </c>
@@ -2469,7 +2497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1869</v>
       </c>
@@ -2507,7 +2535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4049</v>
       </c>
@@ -2536,7 +2564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -2574,7 +2602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2020</v>
       </c>
@@ -2612,7 +2640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1740</v>
       </c>
@@ -2650,7 +2678,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2038</v>
       </c>
@@ -2676,7 +2704,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2022</v>
       </c>
@@ -2708,7 +2736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2039</v>
       </c>
@@ -2743,7 +2771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>3382</v>
       </c>
@@ -2772,7 +2800,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>3853</v>
       </c>
@@ -2804,7 +2832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>4185</v>
       </c>
@@ -2839,7 +2867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>4186</v>
       </c>
@@ -2868,7 +2896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>3854</v>
       </c>
@@ -2903,7 +2931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>3855</v>
       </c>
@@ -2935,7 +2963,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>3387</v>
       </c>
@@ -2961,7 +2989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>3351</v>
       </c>
@@ -2999,7 +3027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>4462</v>
       </c>
@@ -3031,7 +3059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>4463</v>
       </c>
@@ -3057,7 +3085,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>4461</v>
       </c>
@@ -3086,7 +3114,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>3158</v>
       </c>
@@ -3115,7 +3143,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>3159</v>
       </c>
@@ -3144,7 +3172,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>5650</v>
       </c>
@@ -3173,7 +3201,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>5649</v>
       </c>
@@ -3202,7 +3230,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2037</v>
       </c>
@@ -3240,7 +3268,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>3852</v>
       </c>
@@ -3269,7 +3297,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>4370</v>
       </c>
@@ -3295,7 +3323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>5113</v>
       </c>
@@ -3321,7 +3349,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>5647</v>
       </c>
@@ -3356,7 +3384,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>5645</v>
       </c>
@@ -3391,7 +3419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>5646</v>
       </c>
@@ -3426,7 +3454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>4046</v>
       </c>
@@ -3464,7 +3492,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>3882</v>
       </c>
@@ -3496,7 +3524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1763</v>
       </c>
@@ -3525,7 +3553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2029</v>
       </c>
@@ -3551,7 +3579,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2031</v>
       </c>
@@ -3589,7 +3617,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>4190</v>
       </c>
@@ -3615,7 +3643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>3724</v>
       </c>
@@ -3644,4 +3672,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{8b77875e-5908-45a0-9cb4-dec9ae074618}" enabled="1" method="Privileged" siteId="{0f9e35db-544f-4f60-bdcc-5ea416e6dc70}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Data/indicator_metadata.xlsx
+++ b/Data/indicator_metadata.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitednations-my.sharepoint.com/personal/alexis_athens_un_org/Documents/Documentos/CEPALSTAT Data Process/cepalstat-data-upload/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_789E1D78E5C9F4C8A6074CE1C33EC7942A4ABFD4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25DAAB18-81DB-45F0-BC2E-10DFD4D7B1DA}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_12D7453E75FACAE84BE792673F6D76C005BD3D46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B312982F-0B5A-40BB-8D00-0C42DB19EA69}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="28815" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metadata!$A$1:$K$84</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="183">
   <si>
     <t>id</t>
   </si>
@@ -37,16 +40,10 @@
     <t>cat3</t>
   </si>
   <si>
-    <t>source_id</t>
-  </si>
-  <si>
     <t>source</t>
   </si>
   <si>
-    <t>dim_id</t>
-  </si>
-  <si>
-    <t>dimension</t>
+    <t>dimensions</t>
   </si>
   <si>
     <t>yearbook</t>
@@ -94,16 +91,13 @@
     <t>sdg</t>
   </si>
   <si>
-    <t>Country area, by area type</t>
+    <t>Country area</t>
   </si>
   <si>
     <t>Geological and geographical information</t>
   </si>
   <si>
-    <t>21899</t>
-  </si>
-  <si>
-    <t>Area type</t>
+    <t>Type of area</t>
   </si>
   <si>
     <t>Area of inland waters</t>
@@ -139,9 +133,6 @@
     <t>ECLAC</t>
   </si>
   <si>
-    <t>223655; 224796</t>
-  </si>
-  <si>
     <t>Land coverage; Minor administrative division</t>
   </si>
   <si>
@@ -151,9 +142,6 @@
     <t>Landscape heterogeneity index (subnational)</t>
   </si>
   <si>
-    <t>224796</t>
-  </si>
-  <si>
     <t>Minor administrative division</t>
   </si>
   <si>
@@ -178,10 +166,7 @@
     <t>Forests</t>
   </si>
   <si>
-    <t>20722</t>
-  </si>
-  <si>
-    <t>Forest type</t>
+    <t>Type of forest</t>
   </si>
   <si>
     <t>Forest area as a proportion of total land area, by type of forest</t>
@@ -196,7 +181,8 @@
     <t>Forest extent (subnational)</t>
   </si>
   <si>
-    <t>Extent of forest loss (subnational)</t>
+    <t xml:space="preserve">Extent of forest loss (subnational)
+</t>
   </si>
   <si>
     <t>Extent of forest gain (subnational)</t>
@@ -214,9 +200,6 @@
     <t>Air quality</t>
   </si>
   <si>
-    <t>74476</t>
-  </si>
-  <si>
     <t>Location</t>
   </si>
   <si>
@@ -226,7 +209,7 @@
     <t>Fresh water quality</t>
   </si>
   <si>
-    <t>Energy production, by energy product</t>
+    <t>Energy production</t>
   </si>
   <si>
     <t>Environmental resources and their use</t>
@@ -238,43 +221,37 @@
     <t>Production, trade and consumption of energy</t>
   </si>
   <si>
-    <t>OLACDE</t>
-  </si>
-  <si>
-    <t>44966</t>
-  </si>
-  <si>
-    <t>Energy product by primary/secondary</t>
+    <t>OLADE</t>
+  </si>
+  <si>
+    <t>Type of energy__Primary_and_Secondary</t>
   </si>
   <si>
     <t>this used to be indicator 2040</t>
   </si>
   <si>
-    <t>Total energy supply, by energy product</t>
-  </si>
-  <si>
-    <t>Final energy consumption, by energy product</t>
+    <t>Primary and secondary energy supply</t>
+  </si>
+  <si>
+    <t>Final energy consumption</t>
   </si>
   <si>
     <t>this used to be indicator 2041</t>
   </si>
   <si>
-    <t>Primary energy supply from renewable and non-renewable sources, by energy product</t>
+    <t>Primary energy supply from renewable and non-renewable sources, by type of energy</t>
   </si>
   <si>
     <t>Renewable energy</t>
   </si>
   <si>
-    <t>44959</t>
-  </si>
-  <si>
-    <t>Energy product by renewability</t>
+    <t>Renewable and non-renewable primary energy type</t>
   </si>
   <si>
     <t>Renewable energy share of primary energy supply</t>
   </si>
   <si>
-    <t>Composition of renewable primary energy supply, by energy product</t>
+    <t>Composition of renewable primary energy supply, by type of energy</t>
   </si>
   <si>
     <t>Renewable energy share in the total final energy consumption (%) EG_FEC_RNEW</t>
@@ -298,10 +275,7 @@
     <t>Energy intensity measured in terms of final energy consumption and GDP, by economic activity</t>
   </si>
   <si>
-    <t>78134</t>
-  </si>
-  <si>
-    <t>Economic activity</t>
+    <t>Energy intensity_Economic activity</t>
   </si>
   <si>
     <t>Installed electricity-generating capacity, by energy source</t>
@@ -310,10 +284,7 @@
     <t>Electricity</t>
   </si>
   <si>
-    <t>77605</t>
-  </si>
-  <si>
-    <t>Electricity source</t>
+    <t>Type of energy source</t>
   </si>
   <si>
     <t>Installed electricity-generating capacity (historical series)</t>
@@ -331,7 +302,7 @@
     <t>Electricity losses as a proportion of total electricity supply</t>
   </si>
   <si>
-    <t>Public investment in renewable energy, by energy source</t>
+    <t>Public investment in renewable energy</t>
   </si>
   <si>
     <t>Energy investment and subsidies</t>
@@ -340,10 +311,7 @@
     <t>IRENA</t>
   </si>
   <si>
-    <t>78139</t>
-  </si>
-  <si>
-    <t>Renewable energy type</t>
+    <t>Type of renewable energy</t>
   </si>
   <si>
     <t>Fossil-fuel subsidies (consumption and production) (billions of nominal United States dollars) ER_FFS_CMPT_CD</t>
@@ -367,16 +335,16 @@
     <t>Agricultural area, by type of land use</t>
   </si>
   <si>
-    <t>26646</t>
-  </si>
-  <si>
-    <t>Agricultural land type</t>
+    <t>Type of agricultural land</t>
   </si>
   <si>
     <t>Proportion of agricultural area under organic farming</t>
   </si>
   <si>
-    <t>Capture fisheries production, by fishery type</t>
+    <t>CRED</t>
+  </si>
+  <si>
+    <t>Capture fisheries production</t>
   </si>
   <si>
     <t>Biological resources</t>
@@ -385,30 +353,21 @@
     <t>Aquatic resources</t>
   </si>
   <si>
-    <t>20720</t>
-  </si>
-  <si>
-    <t>Fishery type</t>
-  </si>
-  <si>
-    <t>Aquaculture production, by water type</t>
-  </si>
-  <si>
-    <t>26819</t>
-  </si>
-  <si>
-    <t>Water type</t>
-  </si>
-  <si>
-    <t>Harvested area, by crop</t>
+    <t>Type of fishery</t>
+  </si>
+  <si>
+    <t>Aquaculture production</t>
+  </si>
+  <si>
+    <t>Aquaculture production area</t>
+  </si>
+  <si>
+    <t>Harvested area of main crops</t>
   </si>
   <si>
     <t>Crops</t>
   </si>
   <si>
-    <t>20721</t>
-  </si>
-  <si>
     <t>Crop</t>
   </si>
   <si>
@@ -418,13 +377,10 @@
     <t>Fertilizer use intensity</t>
   </si>
   <si>
-    <t>Pesticide consumption, by type of pesticide</t>
-  </si>
-  <si>
-    <t>20723</t>
-  </si>
-  <si>
-    <t>Pesticide type</t>
+    <t>Pesticide consumption</t>
+  </si>
+  <si>
+    <t>Type of Pesticide</t>
   </si>
   <si>
     <t>Pesticide use intensity</t>
@@ -436,9 +392,6 @@
     <t>Water resources</t>
   </si>
   <si>
-    <t>77571</t>
-  </si>
-  <si>
     <t>Activity</t>
   </si>
   <si>
@@ -448,10 +401,7 @@
     <t>Abstraction, use and returns of water</t>
   </si>
   <si>
-    <t>59252</t>
-  </si>
-  <si>
-    <t>Sector_Water</t>
+    <t>Sector__Water resources</t>
   </si>
   <si>
     <t>Water intensity of agricultural value added</t>
@@ -463,9 +413,6 @@
     <t>Degree of integrated water resources management implementation (%) ER_H2O_IWRMD</t>
   </si>
   <si>
-    <t>74666</t>
-  </si>
-  <si>
     <t>Level/Status</t>
   </si>
   <si>
@@ -481,25 +428,19 @@
     <t>Emissions of greenhouse gases (GHGs)</t>
   </si>
   <si>
-    <t>WRI</t>
+    <t>CAIT - WRI</t>
   </si>
   <si>
     <t>Greenhouse gas (GHG) emissions, by sector</t>
   </si>
   <si>
-    <t>63371</t>
-  </si>
-  <si>
-    <t>Sector_GHG</t>
-  </si>
-  <si>
-    <t>Greenhouse gas (GHG) emissions, by energy subsector</t>
-  </si>
-  <si>
-    <t>84302</t>
-  </si>
-  <si>
-    <t>Energy subsector</t>
+    <t>Greenhouse Gas (GHG) Emissions by sector</t>
+  </si>
+  <si>
+    <t>Greenhouse gas (GHG) emissions from the energy sector</t>
+  </si>
+  <si>
+    <t>Greenhouse Gas (GHG) Emissions of the energy sector</t>
   </si>
   <si>
     <t>Greenhouse gas (GHG) emissions per unit of GDP</t>
@@ -508,7 +449,7 @@
     <t>Greenhouse gas (GHG) emissions per capita</t>
   </si>
   <si>
-    <t>Carbon dioxide (CO2) emissions excluding land-use change and forestry</t>
+    <t>Carbon dioxide (CO2) emissions, excluding land-use change and forestry</t>
   </si>
   <si>
     <t>Share of global carbon dioxide (CO2) emissions</t>
@@ -520,7 +461,7 @@
     <t>Carbon dioxide (CO2) emissions per capita</t>
   </si>
   <si>
-    <t>Consumption of ozone-depleting substances (ODS), by ODS</t>
+    <t>Consumption of all ozone-depleting substances (ODS)</t>
   </si>
   <si>
     <t>Consumption of ozone depleting substances (ODS)</t>
@@ -529,10 +470,7 @@
     <t>UNEP</t>
   </si>
   <si>
-    <t>26657</t>
-  </si>
-  <si>
-    <t>Ozone-depleting substance</t>
+    <t>Type of ozone depleting substances (ODS)</t>
   </si>
   <si>
     <t>Proportion of safely treated domestic wastewater flows (%) EN_WWT_WWDS</t>
@@ -568,13 +506,7 @@
     <t>Occurrence of natural extreme events and disasters</t>
   </si>
   <si>
-    <t>CRED</t>
-  </si>
-  <si>
-    <t>21714</t>
-  </si>
-  <si>
-    <t>Disaster type</t>
+    <t>Type of disaster</t>
   </si>
   <si>
     <t>Number of deaths attributed to disasters, by type of disaster</t>
@@ -586,7 +518,8 @@
     <t>Number of directly affected persons attributed to disasters, by type of disaster</t>
   </si>
   <si>
-    <t>Economic loss attributed to disasters, by type of disaster</t>
+    <t xml:space="preserve">Economic loss attributed to disasters, by type of disaster
+</t>
   </si>
   <si>
     <t>Proportion of population with primary reliance on clean fuels and technology (%) EG_EGY_CLEAN</t>
@@ -619,16 +552,13 @@
     <t>ISO 14001-certified enterprises per unit of GDP</t>
   </si>
   <si>
-    <t>Multilateral environmental agreements, by status</t>
+    <t>Multilateral environmental agreements</t>
   </si>
   <si>
     <t>Participation in MEAs and environmental conventions</t>
   </si>
   <si>
     <t>InforMEA</t>
-  </si>
-  <si>
-    <t>26667; 26689</t>
   </si>
   <si>
     <t>Multilateral environmental agreements; Signature, party, entry into force</t>
@@ -650,7 +580,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,13 +592,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -694,12 +617,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,10 +637,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1008,10 +926,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M84"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="33.453125" customWidth="1"/>
+    <col min="3" max="3" width="18.08984375" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,2631 +970,2275 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3381</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>651</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>4501</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="F3">
-        <v>7189</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2035</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>651</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2054</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5">
-        <v>651</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3974</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>9083</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4176</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>651</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2016</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8">
-        <v>876</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3355</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>651</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>5417</v>
       </c>
       <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10">
-        <v>9362</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>5418</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11">
-        <v>9362</v>
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>3963</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12">
-        <v>15911</v>
-      </c>
-      <c r="G12" t="s">
-        <v>22</v>
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3967</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13">
-        <v>15911</v>
-      </c>
-      <c r="G13" t="s">
-        <v>22</v>
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>3968</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14">
-        <v>15911</v>
-      </c>
-      <c r="G14" t="s">
-        <v>22</v>
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3979</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15">
-        <v>5154</v>
-      </c>
-      <c r="G15" t="s">
-        <v>22</v>
+        <v>41</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="L15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2036</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16">
-        <v>651</v>
+        <v>46</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2021</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17">
-        <v>1338</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I17" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2530</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18">
-        <v>1338</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2531</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19">
-        <v>5174</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
+        <v>46</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>5423</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20">
-        <v>9362</v>
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" t="s">
-        <v>44</v>
-      </c>
-      <c r="L20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="J20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>5424</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21">
-        <v>9362</v>
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" t="s">
-        <v>44</v>
-      </c>
-      <c r="L21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="J21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>5425</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22">
-        <v>9362</v>
+        <v>46</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="J22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>5422</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23">
-        <v>9362</v>
+        <v>46</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" t="s">
-        <v>44</v>
-      </c>
-      <c r="L23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="J23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>3946</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
-      </c>
-      <c r="F24">
-        <v>5188</v>
+        <v>57</v>
+      </c>
+      <c r="F24" t="s">
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>3850</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25">
-        <v>9747</v>
-      </c>
-      <c r="G25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>5672</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26">
-        <v>714</v>
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
+        <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" t="s">
-        <v>73</v>
-      </c>
-      <c r="I26" t="s">
-        <v>74</v>
-      </c>
-      <c r="L26" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="J26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2487</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27">
-        <v>714</v>
+        <v>64</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H27" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" t="s">
-        <v>18</v>
-      </c>
-      <c r="L27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>5730</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" t="s">
+        <v>66</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" t="s">
         <v>70</v>
       </c>
-      <c r="E28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28">
-        <v>714</v>
-      </c>
-      <c r="G28" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" t="s">
-        <v>73</v>
-      </c>
-      <c r="I28" t="s">
-        <v>74</v>
-      </c>
-      <c r="L28" t="s">
-        <v>19</v>
-      </c>
-      <c r="M28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2486</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29">
-        <v>714</v>
+        <v>72</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
       </c>
       <c r="G29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s">
-        <v>81</v>
-      </c>
-      <c r="I29" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
-      </c>
-      <c r="L29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3154</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30">
-        <v>714</v>
-      </c>
-      <c r="G30" t="s">
         <v>72</v>
       </c>
+      <c r="F30" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
       <c r="J30" t="s">
-        <v>18</v>
-      </c>
-      <c r="L30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>4236</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
-      </c>
-      <c r="F31">
-        <v>714</v>
+        <v>72</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
-      </c>
-      <c r="K31" t="s">
-        <v>18</v>
-      </c>
-      <c r="L31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>3883</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32">
-        <v>16027</v>
-      </c>
-      <c r="G32" t="s">
-        <v>22</v>
+        <v>72</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
-      </c>
-      <c r="K32" t="s">
-        <v>18</v>
-      </c>
-      <c r="L32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>4174</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33">
-        <v>885</v>
-      </c>
-      <c r="G33" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+      <c r="F33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>16</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
-      </c>
-      <c r="K33" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>4183</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34">
-        <v>10685</v>
-      </c>
-      <c r="G34" t="s">
-        <v>72</v>
-      </c>
-      <c r="K34" t="s">
-        <v>18</v>
-      </c>
-      <c r="L34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="F34" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2023</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E35" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35">
-        <v>714</v>
-      </c>
-      <c r="G35" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+      <c r="F35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>16</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
-      </c>
-      <c r="K35" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>4184</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36">
-        <v>10685</v>
-      </c>
-      <c r="G36" t="s">
-        <v>72</v>
-      </c>
-      <c r="K36" t="s">
-        <v>18</v>
-      </c>
-      <c r="L36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="F36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>4243</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37">
-        <v>885</v>
+        <v>78</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
       </c>
       <c r="G37" t="s">
-        <v>72</v>
-      </c>
-      <c r="H37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
-      </c>
-      <c r="K37" t="s">
-        <v>18</v>
-      </c>
-      <c r="L37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>4150</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38">
-        <v>714</v>
+        <v>85</v>
+      </c>
+      <c r="F38" t="s">
+        <v>65</v>
       </c>
       <c r="G38" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="I38" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38" t="s">
-        <v>18</v>
-      </c>
-      <c r="L38" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1755</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>95</v>
-      </c>
-      <c r="F39">
-        <v>714</v>
-      </c>
-      <c r="G39" t="s">
-        <v>72</v>
+        <v>85</v>
+      </c>
+      <c r="F39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I39" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" t="s">
+        <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>18</v>
-      </c>
-      <c r="L39" t="s">
-        <v>19</v>
-      </c>
-      <c r="M39" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1754</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
-      </c>
-      <c r="F40">
-        <v>714</v>
-      </c>
-      <c r="G40" t="s">
-        <v>72</v>
+        <v>85</v>
+      </c>
+      <c r="F40" t="s">
+        <v>65</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>16</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40" t="s">
-        <v>18</v>
-      </c>
-      <c r="L40" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>4234</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
-      </c>
-      <c r="F41">
-        <v>714</v>
-      </c>
-      <c r="G41" t="s">
-        <v>72</v>
-      </c>
-      <c r="K41" t="s">
-        <v>18</v>
-      </c>
-      <c r="L41" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+      <c r="I41" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>4235</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
-      </c>
-      <c r="F42">
-        <v>714</v>
-      </c>
-      <c r="G42" t="s">
-        <v>72</v>
+        <v>85</v>
+      </c>
+      <c r="F42" t="s">
+        <v>65</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s">
+        <v>16</v>
       </c>
       <c r="J42" t="s">
-        <v>18</v>
-      </c>
-      <c r="K42" t="s">
-        <v>18</v>
-      </c>
-      <c r="L42" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>4244</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>104</v>
-      </c>
-      <c r="F43">
-        <v>10686</v>
+        <v>93</v>
+      </c>
+      <c r="F43" t="s">
+        <v>94</v>
       </c>
       <c r="G43" t="s">
-        <v>105</v>
-      </c>
-      <c r="H43" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I43" t="s">
-        <v>107</v>
-      </c>
-      <c r="K43" t="s">
-        <v>18</v>
-      </c>
-      <c r="L43" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4826</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E44" t="s">
-        <v>104</v>
-      </c>
-      <c r="F44">
-        <v>9461</v>
-      </c>
-      <c r="G44" t="s">
-        <v>22</v>
-      </c>
-      <c r="L44" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4375</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
-      </c>
-      <c r="F45">
-        <v>16068</v>
-      </c>
-      <c r="G45" t="s">
-        <v>22</v>
-      </c>
-      <c r="L45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4827</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>104</v>
-      </c>
-      <c r="F46">
-        <v>5676</v>
-      </c>
-      <c r="G46" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1739</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>113</v>
-      </c>
-      <c r="F47">
-        <v>651</v>
-      </c>
-      <c r="G47" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1869</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>113</v>
-      </c>
-      <c r="F48">
-        <v>651</v>
+        <v>101</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="H48" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="I48" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="J48" t="s">
-        <v>18</v>
-      </c>
-      <c r="K48" t="s">
-        <v>18</v>
-      </c>
-      <c r="L48" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4049</v>
       </c>
       <c r="B49" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>113</v>
-      </c>
-      <c r="F49">
-        <v>651</v>
-      </c>
-      <c r="G49" t="s">
-        <v>17</v>
+        <v>101</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
       </c>
       <c r="J49" t="s">
-        <v>18</v>
-      </c>
-      <c r="L49" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2019</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D50" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E50" t="s">
-        <v>120</v>
-      </c>
-      <c r="F50">
-        <v>877</v>
+        <v>108</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H50" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="I50" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="J50" t="s">
-        <v>18</v>
-      </c>
-      <c r="K50" t="s">
-        <v>18</v>
-      </c>
-      <c r="L50" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2020</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E51" t="s">
-        <v>120</v>
-      </c>
-      <c r="F51">
-        <v>877</v>
+        <v>108</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="H51" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="I51" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="J51" t="s">
-        <v>18</v>
-      </c>
-      <c r="K51" t="s">
-        <v>18</v>
-      </c>
-      <c r="L51" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1740</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F52">
-        <v>651</v>
+        <v>113</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="H52" t="s">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="I52" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="J52" t="s">
-        <v>18</v>
-      </c>
-      <c r="K52" t="s">
-        <v>18</v>
-      </c>
-      <c r="L52" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2038</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E53" t="s">
-        <v>127</v>
-      </c>
-      <c r="F53">
-        <v>651</v>
-      </c>
-      <c r="G53" t="s">
-        <v>17</v>
-      </c>
-      <c r="L53" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="F53" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2022</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F54">
-        <v>913</v>
-      </c>
-      <c r="G54" t="s">
-        <v>38</v>
+        <v>113</v>
+      </c>
+      <c r="F54" t="s">
+        <v>35</v>
+      </c>
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s">
+        <v>16</v>
       </c>
       <c r="J54" t="s">
-        <v>18</v>
-      </c>
-      <c r="K54" t="s">
-        <v>18</v>
-      </c>
-      <c r="L54" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2039</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
-      </c>
-      <c r="F55">
-        <v>1827</v>
+        <v>113</v>
+      </c>
+      <c r="F55" t="s">
+        <v>35</v>
       </c>
       <c r="G55" t="s">
-        <v>38</v>
-      </c>
-      <c r="H55" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="I55" t="s">
-        <v>134</v>
-      </c>
-      <c r="K55" t="s">
-        <v>18</v>
-      </c>
-      <c r="L55" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="J55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>3382</v>
       </c>
       <c r="B56" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E56" t="s">
-        <v>127</v>
-      </c>
-      <c r="F56">
-        <v>1827</v>
-      </c>
-      <c r="G56" t="s">
-        <v>38</v>
+        <v>113</v>
+      </c>
+      <c r="F56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
       </c>
       <c r="J56" t="s">
-        <v>18</v>
-      </c>
-      <c r="L56" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>3853</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E57" t="s">
-        <v>137</v>
-      </c>
-      <c r="F57">
-        <v>3713</v>
+        <v>121</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" t="s">
-        <v>138</v>
-      </c>
-      <c r="I57" t="s">
-        <v>139</v>
-      </c>
-      <c r="L57" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+      <c r="J57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>4185</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E58" t="s">
-        <v>141</v>
-      </c>
-      <c r="F58">
-        <v>5173</v>
+        <v>124</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="H58" t="s">
-        <v>142</v>
-      </c>
-      <c r="I58" t="s">
-        <v>143</v>
+        <v>16</v>
       </c>
       <c r="J58" t="s">
-        <v>18</v>
-      </c>
-      <c r="L58" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>4186</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C59" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E59" t="s">
-        <v>141</v>
-      </c>
-      <c r="F59">
-        <v>1743</v>
-      </c>
-      <c r="G59" t="s">
-        <v>17</v>
+        <v>124</v>
+      </c>
+      <c r="F59" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" t="s">
+        <v>16</v>
       </c>
       <c r="J59" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>3854</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E60" t="s">
-        <v>141</v>
-      </c>
-      <c r="F60">
-        <v>3713</v>
+        <v>124</v>
+      </c>
+      <c r="F60" t="s">
+        <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="H60" t="s">
-        <v>138</v>
-      </c>
-      <c r="I60" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="J60" t="s">
-        <v>18</v>
-      </c>
-      <c r="L60" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>3855</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D61" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E61" t="s">
-        <v>141</v>
-      </c>
-      <c r="F61">
-        <v>5439</v>
+        <v>124</v>
+      </c>
+      <c r="F61" t="s">
+        <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" t="s">
-        <v>147</v>
-      </c>
-      <c r="I61" t="s">
-        <v>148</v>
-      </c>
-      <c r="L61" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+      <c r="J61" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>3387</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D62" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E62" t="s">
-        <v>152</v>
-      </c>
-      <c r="F62">
-        <v>1742</v>
-      </c>
-      <c r="G62" t="s">
-        <v>153</v>
-      </c>
-      <c r="L62" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="F62" t="s">
+        <v>134</v>
+      </c>
+      <c r="J62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>3351</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C63" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D63" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E63" t="s">
-        <v>152</v>
-      </c>
-      <c r="F63">
-        <v>1742</v>
+        <v>133</v>
+      </c>
+      <c r="F63" t="s">
+        <v>134</v>
       </c>
       <c r="G63" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H63" t="s">
-        <v>155</v>
+        <v>16</v>
       </c>
       <c r="I63" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="J63" t="s">
-        <v>18</v>
-      </c>
-      <c r="K63" t="s">
-        <v>18</v>
-      </c>
-      <c r="L63" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>4462</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D64" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E64" t="s">
-        <v>152</v>
-      </c>
-      <c r="F64">
-        <v>1742</v>
+        <v>133</v>
+      </c>
+      <c r="F64" t="s">
+        <v>134</v>
       </c>
       <c r="G64" t="s">
-        <v>153</v>
-      </c>
-      <c r="H64" t="s">
-        <v>158</v>
-      </c>
-      <c r="I64" t="s">
-        <v>159</v>
-      </c>
-      <c r="L64" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+      <c r="J64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>4463</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D65" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E65" t="s">
-        <v>152</v>
-      </c>
-      <c r="F65">
-        <v>10621</v>
-      </c>
-      <c r="G65" t="s">
-        <v>153</v>
-      </c>
-      <c r="L65" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="F65" t="s">
+        <v>134</v>
+      </c>
+      <c r="J65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>4461</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="C66" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D66" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E66" t="s">
-        <v>152</v>
-      </c>
-      <c r="F66">
-        <v>10621</v>
-      </c>
-      <c r="G66" t="s">
-        <v>153</v>
-      </c>
-      <c r="K66" t="s">
-        <v>18</v>
-      </c>
-      <c r="L66" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="F66" t="s">
+        <v>134</v>
+      </c>
+      <c r="I66" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>3158</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D67" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E67" t="s">
-        <v>152</v>
-      </c>
-      <c r="F67">
-        <v>1742</v>
-      </c>
-      <c r="G67" t="s">
-        <v>153</v>
+        <v>133</v>
+      </c>
+      <c r="F67" t="s">
+        <v>134</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
       </c>
       <c r="J67" t="s">
-        <v>18</v>
-      </c>
-      <c r="L67" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>3159</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D68" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E68" t="s">
-        <v>152</v>
-      </c>
-      <c r="F68">
-        <v>1742</v>
-      </c>
-      <c r="G68" t="s">
-        <v>153</v>
+        <v>133</v>
+      </c>
+      <c r="F68" t="s">
+        <v>134</v>
+      </c>
+      <c r="H68" t="s">
+        <v>16</v>
       </c>
       <c r="J68" t="s">
-        <v>18</v>
-      </c>
-      <c r="L68" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>5650</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="C69" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D69" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E69" t="s">
-        <v>152</v>
-      </c>
-      <c r="F69">
-        <v>10621</v>
-      </c>
-      <c r="G69" t="s">
-        <v>153</v>
+        <v>133</v>
+      </c>
+      <c r="F69" t="s">
+        <v>134</v>
+      </c>
+      <c r="H69" t="s">
+        <v>16</v>
       </c>
       <c r="J69" t="s">
-        <v>18</v>
-      </c>
-      <c r="L69" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>5649</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D70" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E70" t="s">
-        <v>152</v>
-      </c>
-      <c r="F70">
-        <v>10621</v>
-      </c>
-      <c r="G70" t="s">
-        <v>153</v>
+        <v>133</v>
+      </c>
+      <c r="F70" t="s">
+        <v>134</v>
+      </c>
+      <c r="H70" t="s">
+        <v>16</v>
       </c>
       <c r="J70" t="s">
-        <v>18</v>
-      </c>
-      <c r="L70" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2037</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E71" t="s">
-        <v>167</v>
-      </c>
-      <c r="F71">
-        <v>630</v>
+        <v>146</v>
+      </c>
+      <c r="F71" t="s">
+        <v>147</v>
       </c>
       <c r="G71" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="H71" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="I71" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="J71" t="s">
-        <v>18</v>
-      </c>
-      <c r="K71" t="s">
-        <v>18</v>
-      </c>
-      <c r="L71" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>3852</v>
       </c>
       <c r="B72" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
+        <v>131</v>
+      </c>
+      <c r="D72" t="s">
         <v>150</v>
       </c>
-      <c r="D72" t="s">
-        <v>172</v>
-      </c>
       <c r="E72" t="s">
-        <v>173</v>
-      </c>
-      <c r="F72">
-        <v>5437</v>
-      </c>
-      <c r="G72" t="s">
-        <v>22</v>
+        <v>151</v>
+      </c>
+      <c r="F72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" t="s">
+        <v>16</v>
       </c>
       <c r="J72" t="s">
-        <v>18</v>
-      </c>
-      <c r="L72" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>4370</v>
       </c>
       <c r="B73" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D73" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="E73" t="s">
-        <v>176</v>
-      </c>
-      <c r="F73">
-        <v>9833</v>
-      </c>
-      <c r="G73" t="s">
-        <v>22</v>
-      </c>
-      <c r="L73" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+      <c r="F73" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>5113</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="C74" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D74" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="E74" t="s">
-        <v>176</v>
-      </c>
-      <c r="F74">
-        <v>8631</v>
-      </c>
-      <c r="G74" t="s">
-        <v>22</v>
-      </c>
-      <c r="L74" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+      <c r="F74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>5647</v>
       </c>
       <c r="B75" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="C75" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="D75" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E75" t="s">
-        <v>181</v>
-      </c>
-      <c r="F75">
-        <v>742</v>
+        <v>159</v>
+      </c>
+      <c r="F75" t="s">
+        <v>105</v>
       </c>
       <c r="G75" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="H75" t="s">
-        <v>183</v>
-      </c>
-      <c r="I75" t="s">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="J75" t="s">
-        <v>18</v>
-      </c>
-      <c r="L75" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>5645</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C76" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="D76" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
-      </c>
-      <c r="F76">
-        <v>742</v>
+        <v>162</v>
+      </c>
+      <c r="F76" t="s">
+        <v>105</v>
       </c>
       <c r="G76" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="H76" t="s">
-        <v>183</v>
-      </c>
-      <c r="I76" t="s">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="J76" t="s">
-        <v>18</v>
-      </c>
-      <c r="L76" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>5646</v>
       </c>
       <c r="B77" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="C77" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="D77" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E77" t="s">
-        <v>186</v>
-      </c>
-      <c r="F77">
-        <v>742</v>
+        <v>162</v>
+      </c>
+      <c r="F77" t="s">
+        <v>105</v>
       </c>
       <c r="G77" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="H77" t="s">
-        <v>183</v>
-      </c>
-      <c r="I77" t="s">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="J77" t="s">
-        <v>18</v>
-      </c>
-      <c r="L77" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>4046</v>
       </c>
       <c r="B78" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C78" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="D78" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E78" t="s">
-        <v>186</v>
-      </c>
-      <c r="F78">
-        <v>742</v>
+        <v>162</v>
+      </c>
+      <c r="F78" t="s">
+        <v>105</v>
       </c>
       <c r="G78" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="H78" t="s">
-        <v>183</v>
+        <v>16</v>
       </c>
       <c r="I78" t="s">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="J78" t="s">
-        <v>18</v>
-      </c>
-      <c r="K78" t="s">
-        <v>18</v>
-      </c>
-      <c r="L78" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>3882</v>
       </c>
       <c r="B79" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="C79" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="D79" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="E79" t="s">
-        <v>192</v>
-      </c>
-      <c r="F79">
-        <v>3719</v>
+        <v>168</v>
+      </c>
+      <c r="F79" t="s">
+        <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" t="s">
-        <v>64</v>
-      </c>
-      <c r="I79" t="s">
-        <v>65</v>
-      </c>
-      <c r="L79" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="J79" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1763</v>
       </c>
       <c r="B80" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C80" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="E80" t="s">
-        <v>196</v>
-      </c>
-      <c r="F80">
-        <v>749</v>
-      </c>
-      <c r="G80" t="s">
-        <v>197</v>
-      </c>
-      <c r="K80" t="s">
-        <v>18</v>
-      </c>
-      <c r="L80" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+      <c r="F80" t="s">
+        <v>173</v>
+      </c>
+      <c r="I80" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2029</v>
       </c>
       <c r="B81" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="D81" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="E81" t="s">
-        <v>196</v>
-      </c>
-      <c r="F81">
-        <v>882</v>
-      </c>
-      <c r="G81" t="s">
-        <v>197</v>
-      </c>
-      <c r="L81" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+      <c r="F81" t="s">
+        <v>35</v>
+      </c>
+      <c r="J81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2031</v>
       </c>
       <c r="B82" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="E82" t="s">
-        <v>200</v>
-      </c>
-      <c r="F82">
-        <v>11306</v>
+        <v>176</v>
+      </c>
+      <c r="F82" t="s">
+        <v>177</v>
       </c>
       <c r="G82" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="H82" t="s">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="I82" t="s">
-        <v>203</v>
+        <v>16</v>
       </c>
       <c r="J82" t="s">
-        <v>18</v>
-      </c>
-      <c r="K82" t="s">
-        <v>18</v>
-      </c>
-      <c r="L82" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>4190</v>
       </c>
       <c r="B83" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="D83" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="E83" t="s">
-        <v>206</v>
-      </c>
-      <c r="F83">
-        <v>16002</v>
-      </c>
-      <c r="G83" t="s">
-        <v>22</v>
-      </c>
-      <c r="L83" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+      <c r="F83" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>3724</v>
       </c>
       <c r="B84" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C84" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="E84" t="s">
-        <v>206</v>
-      </c>
-      <c r="F84">
-        <v>16002</v>
-      </c>
-      <c r="G84" t="s">
-        <v>22</v>
-      </c>
-      <c r="L84" t="s">
-        <v>23</v>
+        <v>181</v>
+      </c>
+      <c r="F84" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K84" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="env"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
